--- a/分省数据看板（月度）/趋势分析/25年5月.xlsx
+++ b/分省数据看板（月度）/趋势分析/25年5月.xlsx
@@ -531,7 +531,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -551,6 +551,36 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -678,7 +708,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -690,34 +720,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
@@ -802,7 +832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -815,14 +845,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1166,21 +1199,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="4">
-        <v>6256</v>
+        <v>6405</v>
       </c>
       <c r="C2" s="4">
         <v>31205</v>
       </c>
       <c r="D2" s="4">
-        <v>4503</v>
+        <v>4606</v>
       </c>
       <c r="E2" s="5">
-        <f>C2/B2</f>
-        <v>4.98801150895141</v>
+        <v>4.871975019516</v>
       </c>
       <c r="F2" s="6">
-        <f>D2/B2</f>
-        <v>0.719789002557545</v>
+        <v>0.719125683060109</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1188,21 +1219,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="4">
-        <v>6745</v>
+        <v>6906</v>
       </c>
       <c r="C3" s="4">
         <v>20398</v>
       </c>
       <c r="D3" s="4">
-        <v>4913</v>
+        <v>5058</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E35" si="0">C3/B3</f>
-        <v>3.02416604892513</v>
+        <v>2.95366348103099</v>
       </c>
       <c r="F3" s="6">
-        <f t="shared" ref="F3:F35" si="1">D3/B3</f>
-        <v>0.728391401037806</v>
+        <v>0.732406602953953</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1210,21 +1239,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="4">
-        <v>7618</v>
+        <v>7791</v>
       </c>
       <c r="C4" s="4">
         <v>13258</v>
       </c>
       <c r="D4" s="4">
-        <v>5062</v>
+        <v>5196</v>
       </c>
       <c r="E4" s="5">
-        <f t="shared" si="0"/>
-        <v>1.74035179837228</v>
+        <v>1.70170709793351</v>
       </c>
       <c r="F4" s="6">
-        <f t="shared" si="1"/>
-        <v>0.664478865844054</v>
+        <v>0.666923373122834</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1232,21 +1259,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="4">
-        <v>3021</v>
+        <v>3084</v>
       </c>
       <c r="C5" s="4">
         <v>6582</v>
       </c>
       <c r="D5" s="4">
-        <v>1981</v>
+        <v>2024</v>
       </c>
       <c r="E5" s="5">
-        <f t="shared" si="0"/>
-        <v>2.17874875868918</v>
+        <v>2.13424124513619</v>
       </c>
       <c r="F5" s="6">
-        <f t="shared" si="1"/>
-        <v>0.655743131413439</v>
+        <v>0.656290531776913</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1254,21 +1279,19 @@
         <v>10</v>
       </c>
       <c r="B6" s="4">
-        <v>2945</v>
+        <v>3037</v>
       </c>
       <c r="C6" s="4">
         <v>9987</v>
       </c>
       <c r="D6" s="4">
-        <v>1892</v>
+        <v>1957</v>
       </c>
       <c r="E6" s="5">
-        <f t="shared" si="0"/>
-        <v>3.3911714770798</v>
+        <v>3.28844254198222</v>
       </c>
       <c r="F6" s="6">
-        <f t="shared" si="1"/>
-        <v>0.642444821731749</v>
+        <v>0.644385907145209</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1276,21 +1299,19 @@
         <v>11</v>
       </c>
       <c r="B7" s="4">
-        <v>11854</v>
+        <v>12131</v>
       </c>
       <c r="C7" s="4">
         <v>47340</v>
       </c>
       <c r="D7" s="4">
-        <v>8814</v>
+        <v>9021</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="0"/>
-        <v>3.993588662055</v>
+        <v>3.90239881295854</v>
       </c>
       <c r="F7" s="6">
-        <f t="shared" si="1"/>
-        <v>0.743546482200101</v>
+        <v>0.743632017146154</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1298,21 +1319,19 @@
         <v>12</v>
       </c>
       <c r="B8" s="4">
-        <v>3489</v>
+        <v>3576</v>
       </c>
       <c r="C8" s="4">
         <v>10902</v>
       </c>
       <c r="D8" s="4">
-        <v>2411</v>
+        <v>2474</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" si="0"/>
-        <v>3.12467755803955</v>
+        <v>3.04865771812081</v>
       </c>
       <c r="F8" s="6">
-        <f t="shared" si="1"/>
-        <v>0.691028948122671</v>
+        <v>0.691834451901566</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1320,21 +1339,19 @@
         <v>13</v>
       </c>
       <c r="B9" s="4">
-        <v>6965</v>
+        <v>7173</v>
       </c>
       <c r="C9" s="4">
         <v>22606</v>
       </c>
       <c r="D9" s="4">
-        <v>4999</v>
+        <v>5162</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="0"/>
-        <v>3.24565685570711</v>
+        <v>3.15154049909382</v>
       </c>
       <c r="F9" s="6">
-        <f t="shared" si="1"/>
-        <v>0.717731514716439</v>
+        <v>0.719643106092291</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1342,21 +1359,19 @@
         <v>14</v>
       </c>
       <c r="B10" s="4">
-        <v>2453</v>
+        <v>2516</v>
       </c>
       <c r="C10" s="4">
         <v>16097</v>
       </c>
       <c r="D10" s="4">
-        <v>1553</v>
+        <v>1591</v>
       </c>
       <c r="E10" s="5">
-        <f t="shared" si="0"/>
-        <v>6.5621687729311</v>
+        <v>6.39785373608903</v>
       </c>
       <c r="F10" s="6">
-        <f t="shared" si="1"/>
-        <v>0.633102323685283</v>
+        <v>0.632352941176471</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1364,21 +1379,19 @@
         <v>15</v>
       </c>
       <c r="B11" s="4">
-        <v>22420</v>
+        <v>22949</v>
       </c>
       <c r="C11" s="4">
         <v>111074</v>
       </c>
       <c r="D11" s="4">
-        <v>15719</v>
+        <v>16139</v>
       </c>
       <c r="E11" s="5">
-        <f t="shared" si="0"/>
-        <v>4.95423728813559</v>
+        <v>4.84003660290209</v>
       </c>
       <c r="F11" s="6">
-        <f t="shared" si="1"/>
-        <v>0.701115075825156</v>
+        <v>0.703255043792758</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1386,21 +1399,19 @@
         <v>16</v>
       </c>
       <c r="B12" s="4">
-        <v>7721</v>
+        <v>7866</v>
       </c>
       <c r="C12" s="4">
         <v>21704</v>
       </c>
       <c r="D12" s="4">
-        <v>5392</v>
+        <v>5514</v>
       </c>
       <c r="E12" s="5">
-        <f t="shared" si="0"/>
-        <v>2.81103484004663</v>
+        <v>2.75921688278668</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="1"/>
-        <v>0.698355135345163</v>
+        <v>0.700991609458429</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1408,21 +1419,19 @@
         <v>17</v>
       </c>
       <c r="B13" s="4">
-        <v>12206</v>
+        <v>12458</v>
       </c>
       <c r="C13" s="4">
         <v>35675</v>
       </c>
       <c r="D13" s="4">
-        <v>8604</v>
+        <v>8795</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="0"/>
-        <v>2.92274291332132</v>
+        <v>2.86362176914432</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="1"/>
-        <v>0.704899229886941</v>
+        <v>0.705972066142238</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1430,21 +1439,19 @@
         <v>18</v>
       </c>
       <c r="B14" s="4">
-        <v>9534</v>
+        <v>9737</v>
       </c>
       <c r="C14" s="4">
         <v>28894</v>
       </c>
       <c r="D14" s="4">
-        <v>6832</v>
+        <v>6995</v>
       </c>
       <c r="E14" s="5">
-        <f t="shared" si="0"/>
-        <v>3.03062722886511</v>
+        <v>2.96744377118209</v>
       </c>
       <c r="F14" s="6">
-        <f t="shared" si="1"/>
-        <v>0.716593245227606</v>
+        <v>0.718393755776933</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1452,21 +1459,19 @@
         <v>19</v>
       </c>
       <c r="B15" s="4">
-        <v>6942</v>
+        <v>7125</v>
       </c>
       <c r="C15" s="4">
         <v>11924</v>
       </c>
       <c r="D15" s="4">
-        <v>4761</v>
+        <v>4896</v>
       </c>
       <c r="E15" s="5">
-        <f t="shared" si="0"/>
-        <v>1.71766061653702</v>
+        <v>1.67354385964912</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="1"/>
-        <v>0.685825410544512</v>
+        <v>0.687157894736842</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1474,21 +1479,19 @@
         <v>20</v>
       </c>
       <c r="B16" s="4">
-        <v>29640</v>
+        <v>30256</v>
       </c>
       <c r="C16" s="4">
         <v>75289</v>
       </c>
       <c r="D16" s="4">
-        <v>21874</v>
+        <v>22411</v>
       </c>
       <c r="E16" s="5">
-        <f t="shared" si="0"/>
-        <v>2.54011470985155</v>
+        <v>2.48839899524061</v>
       </c>
       <c r="F16" s="6">
-        <f t="shared" si="1"/>
-        <v>0.737989203778677</v>
+        <v>0.740712585933369</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1496,21 +1499,19 @@
         <v>21</v>
       </c>
       <c r="B17" s="4">
-        <v>9480</v>
+        <v>9686</v>
       </c>
       <c r="C17" s="4">
         <v>14160</v>
       </c>
       <c r="D17" s="4">
-        <v>6351</v>
+        <v>6514</v>
       </c>
       <c r="E17" s="5">
-        <f t="shared" si="0"/>
-        <v>1.49367088607595</v>
+        <v>1.4619037786496</v>
       </c>
       <c r="F17" s="6">
-        <f t="shared" si="1"/>
-        <v>0.66993670886076</v>
+        <v>0.672517034895726</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1518,21 +1519,19 @@
         <v>22</v>
       </c>
       <c r="B18" s="4">
-        <v>7777</v>
+        <v>7962</v>
       </c>
       <c r="C18" s="4">
         <v>23391</v>
       </c>
       <c r="D18" s="4">
-        <v>5393</v>
+        <v>5527</v>
       </c>
       <c r="E18" s="5">
-        <f t="shared" si="0"/>
-        <v>3.00771505722001</v>
+        <v>2.9378296910324</v>
       </c>
       <c r="F18" s="6">
-        <f t="shared" si="1"/>
-        <v>0.693455059791693</v>
+        <v>0.694172318512936</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1540,21 +1539,19 @@
         <v>23</v>
       </c>
       <c r="B19" s="4">
-        <v>9033</v>
+        <v>9233</v>
       </c>
       <c r="C19" s="4">
         <v>26486</v>
       </c>
       <c r="D19" s="4">
-        <v>6255</v>
+        <v>6418</v>
       </c>
       <c r="E19" s="5">
-        <f t="shared" si="0"/>
-        <v>2.93213771725894</v>
+        <v>2.8686234160078</v>
       </c>
       <c r="F19" s="6">
-        <f t="shared" si="1"/>
-        <v>0.692460976419794</v>
+        <v>0.695115347124445</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1562,21 +1559,19 @@
         <v>24</v>
       </c>
       <c r="B20" s="4">
-        <v>15965</v>
+        <v>16257</v>
       </c>
       <c r="C20" s="4">
         <v>68465</v>
       </c>
       <c r="D20" s="4">
-        <v>11173</v>
+        <v>11408</v>
       </c>
       <c r="E20" s="5">
-        <f t="shared" si="0"/>
-        <v>4.28844347009082</v>
+        <v>4.21141662053269</v>
       </c>
       <c r="F20" s="6">
-        <f t="shared" si="1"/>
-        <v>0.699843407453805</v>
+        <v>0.701728486190564</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1584,21 +1579,19 @@
         <v>25</v>
       </c>
       <c r="B21" s="4">
-        <v>3090</v>
+        <v>3143</v>
       </c>
       <c r="C21" s="4">
         <v>6633</v>
       </c>
       <c r="D21" s="4">
-        <v>2102</v>
+        <v>2143</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="0"/>
-        <v>2.14660194174757</v>
+        <v>2.11040407254216</v>
       </c>
       <c r="F21" s="6">
-        <f t="shared" si="1"/>
-        <v>0.680258899676375</v>
+        <v>0.681832643970729</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1606,21 +1599,19 @@
         <v>26</v>
       </c>
       <c r="B22" s="4">
-        <v>1713</v>
+        <v>1746</v>
       </c>
       <c r="C22" s="4">
         <v>7566</v>
       </c>
       <c r="D22" s="4">
-        <v>1251</v>
+        <v>1286</v>
       </c>
       <c r="E22" s="5">
-        <f t="shared" si="0"/>
-        <v>4.41681260945709</v>
+        <v>4.33333333333333</v>
       </c>
       <c r="F22" s="6">
-        <f t="shared" si="1"/>
-        <v>0.730297723292469</v>
+        <v>0.736540664375716</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1628,21 +1619,19 @@
         <v>27</v>
       </c>
       <c r="B23" s="4">
-        <v>5119</v>
+        <v>5219</v>
       </c>
       <c r="C23" s="4">
         <v>22191</v>
       </c>
       <c r="D23" s="4">
-        <v>3624</v>
+        <v>3708</v>
       </c>
       <c r="E23" s="5">
-        <f t="shared" si="0"/>
-        <v>4.33502637233835</v>
+        <v>4.25196397777352</v>
       </c>
       <c r="F23" s="6">
-        <f t="shared" si="1"/>
-        <v>0.707950771635085</v>
+        <v>0.710480935045028</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1650,21 +1639,19 @@
         <v>28</v>
       </c>
       <c r="B24" s="4">
-        <v>7993</v>
+        <v>8168</v>
       </c>
       <c r="C24" s="4">
         <v>23250</v>
       </c>
       <c r="D24" s="4">
-        <v>5633</v>
+        <v>5774</v>
       </c>
       <c r="E24" s="5">
-        <f t="shared" si="0"/>
-        <v>2.90879519579632</v>
+        <v>2.84647404505387</v>
       </c>
       <c r="F24" s="6">
-        <f t="shared" si="1"/>
-        <v>0.704741648942825</v>
+        <v>0.70690499510284</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1672,21 +1659,19 @@
         <v>29</v>
       </c>
       <c r="B25" s="4">
-        <v>2390</v>
+        <v>2438</v>
       </c>
       <c r="C25" s="4">
         <v>4678</v>
       </c>
       <c r="D25" s="4">
-        <v>1578</v>
+        <v>1607</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="0"/>
-        <v>1.95732217573222</v>
+        <v>1.91878589007383</v>
       </c>
       <c r="F25" s="6">
-        <f t="shared" si="1"/>
-        <v>0.660251046025105</v>
+        <v>0.659146841673503</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1694,21 +1679,19 @@
         <v>30</v>
       </c>
       <c r="B26" s="4">
-        <v>3017</v>
+        <v>3080</v>
       </c>
       <c r="C26" s="4">
         <v>10224</v>
       </c>
       <c r="D26" s="4">
-        <v>1891</v>
+        <v>1945</v>
       </c>
       <c r="E26" s="5">
-        <f t="shared" si="0"/>
-        <v>3.38879681803116</v>
+        <v>3.31948051948052</v>
       </c>
       <c r="F26" s="6">
-        <f t="shared" si="1"/>
-        <v>0.626781571097116</v>
+        <v>0.631493506493506</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1716,21 +1699,19 @@
         <v>31</v>
       </c>
       <c r="B27" s="4">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C27" s="4">
         <v>686</v>
       </c>
       <c r="D27" s="4">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E27" s="5">
-        <f t="shared" si="0"/>
-        <v>3.51794871794872</v>
+        <v>3.46464646464646</v>
       </c>
       <c r="F27" s="6">
-        <f t="shared" si="1"/>
-        <v>0.764102564102564</v>
+        <v>0.762626262626263</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1738,21 +1719,19 @@
         <v>32</v>
       </c>
       <c r="B28" s="4">
-        <v>4296</v>
+        <v>4399</v>
       </c>
       <c r="C28" s="4">
         <v>8546</v>
       </c>
       <c r="D28" s="4">
-        <v>2787</v>
+        <v>2849</v>
       </c>
       <c r="E28" s="5">
-        <f t="shared" si="0"/>
-        <v>1.98929236499069</v>
+        <v>1.94271425323937</v>
       </c>
       <c r="F28" s="6">
-        <f t="shared" si="1"/>
-        <v>0.648743016759777</v>
+        <v>0.64764719254376</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1760,21 +1739,19 @@
         <v>33</v>
       </c>
       <c r="B29" s="4">
-        <v>2742</v>
+        <v>2803</v>
       </c>
       <c r="C29" s="4">
         <v>3944</v>
       </c>
       <c r="D29" s="4">
-        <v>1647</v>
+        <v>1696</v>
       </c>
       <c r="E29" s="5">
-        <f t="shared" si="0"/>
-        <v>1.43836615609044</v>
+        <v>1.40706386014984</v>
       </c>
       <c r="F29" s="6">
-        <f t="shared" si="1"/>
-        <v>0.600656455142232</v>
+        <v>0.605066000713521</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1782,21 +1759,19 @@
         <v>34</v>
       </c>
       <c r="B30" s="4">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="C30" s="4">
         <v>1371</v>
       </c>
       <c r="D30" s="4">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="E30" s="5">
-        <f t="shared" si="0"/>
-        <v>2.15566037735849</v>
+        <v>2.06475903614458</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" si="1"/>
-        <v>0.666666666666667</v>
+        <v>0.674698795180723</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1804,21 +1779,19 @@
         <v>35</v>
       </c>
       <c r="B31" s="4">
-        <v>1089</v>
+        <v>1117</v>
       </c>
       <c r="C31" s="4">
         <v>3059</v>
       </c>
       <c r="D31" s="4">
-        <v>757</v>
+        <v>781</v>
       </c>
       <c r="E31" s="5">
-        <f t="shared" si="0"/>
-        <v>2.80899908172635</v>
+        <v>2.73858549686661</v>
       </c>
       <c r="F31" s="6">
-        <f t="shared" si="1"/>
-        <v>0.695133149678604</v>
+        <v>0.699194270367055</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1826,21 +1799,19 @@
         <v>36</v>
       </c>
       <c r="B32" s="4">
-        <v>3157</v>
+        <v>3256</v>
       </c>
       <c r="C32" s="4">
         <v>7443</v>
       </c>
       <c r="D32" s="4">
-        <v>1863</v>
+        <v>1923</v>
       </c>
       <c r="E32" s="5">
-        <f t="shared" si="0"/>
-        <v>2.35761799176433</v>
+        <v>2.28593366093366</v>
       </c>
       <c r="F32" s="6">
-        <f t="shared" si="1"/>
-        <v>0.590117199873297</v>
+        <v>0.590601965601966</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1848,21 +1819,19 @@
         <v>37</v>
       </c>
       <c r="B33" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C33" s="4">
         <v>268</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="7">
         <v>17</v>
       </c>
       <c r="E33" s="5">
-        <f t="shared" si="0"/>
-        <v>9.57142857142857</v>
+        <v>9.24137931034483</v>
       </c>
       <c r="F33" s="6">
-        <f t="shared" si="1"/>
-        <v>0.607142857142857</v>
+        <v>0.586206896551724</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1872,16 +1841,16 @@
       <c r="B34" s="4">
         <v>11</v>
       </c>
-      <c r="C34" s="4"/>
+      <c r="C34" s="4">
+        <v>0</v>
+      </c>
       <c r="D34" s="4">
         <v>6</v>
       </c>
       <c r="E34" s="5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F34" s="6">
-        <f t="shared" si="1"/>
         <v>0.545454545454545</v>
       </c>
     </row>
@@ -1890,21 +1859,19 @@
         <v>39</v>
       </c>
       <c r="B35" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C35" s="4">
         <v>49</v>
       </c>
       <c r="D35" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E35" s="5">
-        <f t="shared" si="0"/>
-        <v>4.08333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="F35" s="6">
-        <f t="shared" si="1"/>
-        <v>0.833333333333333</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
   </sheetData>

--- a/分省数据看板（月度）/趋势分析/25年5月.xlsx
+++ b/分省数据看板（月度）/趋势分析/25年5月.xlsx
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>名称</t>
   </si>
   <si>
     <t>活跃用户</t>
+  </si>
+  <si>
+    <t>新用户</t>
   </si>
   <si>
     <t>营收</t>
@@ -337,12 +340,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -708,7 +717,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -732,16 +741,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
@@ -750,89 +759,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -848,11 +857,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1168,13 +1183,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="5" max="6" width="12.625"/>
+    <col min="6" max="7" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,687 +1205,792 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4">
         <v>6405</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
+        <v>2293</v>
+      </c>
+      <c r="D2" s="4">
         <v>31205</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="4">
         <v>4606</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="6">
         <v>4.871975019516</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="7">
         <v>0.719125683060109</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4">
         <v>6906</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
+        <v>2535</v>
+      </c>
+      <c r="D3" s="4">
         <v>20398</v>
       </c>
-      <c r="D3" s="4">
+      <c r="E3" s="4">
         <v>5058</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="6">
         <v>2.95366348103099</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="7">
         <v>0.732406602953953</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4">
         <v>7791</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="8">
+        <v>3818</v>
+      </c>
+      <c r="D4" s="4">
         <v>13258</v>
       </c>
-      <c r="D4" s="4">
+      <c r="E4" s="4">
         <v>5196</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="6">
         <v>1.70170709793351</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="7">
         <v>0.666923373122834</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4">
         <v>3084</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
+        <v>1556</v>
+      </c>
+      <c r="D5" s="4">
         <v>6582</v>
       </c>
-      <c r="D5" s="4">
+      <c r="E5" s="4">
         <v>2024</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="6">
         <v>2.13424124513619</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="7">
         <v>0.656290531776913</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4">
         <v>3037</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
+        <v>1516</v>
+      </c>
+      <c r="D6" s="4">
         <v>9987</v>
       </c>
-      <c r="D6" s="4">
+      <c r="E6" s="4">
         <v>1957</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="6">
         <v>3.28844254198222</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="7">
         <v>0.644385907145209</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4">
         <v>12131</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
+        <v>4126</v>
+      </c>
+      <c r="D7" s="4">
         <v>47340</v>
       </c>
-      <c r="D7" s="4">
+      <c r="E7" s="4">
         <v>9021</v>
       </c>
-      <c r="E7" s="5">
+      <c r="F7" s="6">
         <v>3.90239881295854</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="7">
         <v>0.743632017146154</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4">
         <v>3576</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
+        <v>1566</v>
+      </c>
+      <c r="D8" s="4">
         <v>10902</v>
       </c>
-      <c r="D8" s="4">
+      <c r="E8" s="4">
         <v>2474</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="6">
         <v>3.04865771812081</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="7">
         <v>0.691834451901566</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4">
         <v>7173</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
+        <v>2826</v>
+      </c>
+      <c r="D9" s="4">
         <v>22606</v>
       </c>
-      <c r="D9" s="4">
+      <c r="E9" s="4">
         <v>5162</v>
       </c>
-      <c r="E9" s="5">
+      <c r="F9" s="6">
         <v>3.15154049909382</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="7">
         <v>0.719643106092291</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4">
         <v>2516</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
+        <v>1192</v>
+      </c>
+      <c r="D10" s="4">
         <v>16097</v>
       </c>
-      <c r="D10" s="4">
+      <c r="E10" s="4">
         <v>1591</v>
       </c>
-      <c r="E10" s="5">
+      <c r="F10" s="6">
         <v>6.39785373608903</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="7">
         <v>0.632352941176471</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4">
         <v>22949</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
+        <v>10591</v>
+      </c>
+      <c r="D11" s="4">
         <v>111074</v>
       </c>
-      <c r="D11" s="4">
+      <c r="E11" s="4">
         <v>16139</v>
       </c>
-      <c r="E11" s="5">
+      <c r="F11" s="6">
         <v>4.84003660290209</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="7">
         <v>0.703255043792758</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4">
         <v>7866</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
+        <v>3618</v>
+      </c>
+      <c r="D12" s="4">
         <v>21704</v>
       </c>
-      <c r="D12" s="4">
+      <c r="E12" s="4">
         <v>5514</v>
       </c>
-      <c r="E12" s="5">
+      <c r="F12" s="6">
         <v>2.75921688278668</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="7">
         <v>0.700991609458429</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4">
         <v>12458</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
+        <v>4854</v>
+      </c>
+      <c r="D13" s="4">
         <v>35675</v>
       </c>
-      <c r="D13" s="4">
+      <c r="E13" s="4">
         <v>8795</v>
       </c>
-      <c r="E13" s="5">
+      <c r="F13" s="6">
         <v>2.86362176914432</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="7">
         <v>0.705972066142238</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4">
         <v>9737</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
+        <v>3606</v>
+      </c>
+      <c r="D14" s="4">
         <v>28894</v>
       </c>
-      <c r="D14" s="4">
+      <c r="E14" s="4">
         <v>6995</v>
       </c>
-      <c r="E14" s="5">
+      <c r="F14" s="6">
         <v>2.96744377118209</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="7">
         <v>0.718393755776933</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4">
         <v>7125</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
+        <v>3240</v>
+      </c>
+      <c r="D15" s="4">
         <v>11924</v>
       </c>
-      <c r="D15" s="4">
+      <c r="E15" s="4">
         <v>4896</v>
       </c>
-      <c r="E15" s="5">
+      <c r="F15" s="6">
         <v>1.67354385964912</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="7">
         <v>0.687157894736842</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4">
         <v>30256</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
+        <v>11575</v>
+      </c>
+      <c r="D16" s="4">
         <v>75289</v>
       </c>
-      <c r="D16" s="4">
+      <c r="E16" s="4">
         <v>22411</v>
       </c>
-      <c r="E16" s="5">
+      <c r="F16" s="6">
         <v>2.48839899524061</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="7">
         <v>0.740712585933369</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4">
         <v>9686</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
+        <v>4760</v>
+      </c>
+      <c r="D17" s="4">
         <v>14160</v>
       </c>
-      <c r="D17" s="4">
+      <c r="E17" s="4">
         <v>6514</v>
       </c>
-      <c r="E17" s="5">
+      <c r="F17" s="6">
         <v>1.4619037786496</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="7">
         <v>0.672517034895726</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="4">
         <v>7962</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
+        <v>3476</v>
+      </c>
+      <c r="D18" s="4">
         <v>23391</v>
       </c>
-      <c r="D18" s="4">
+      <c r="E18" s="4">
         <v>5527</v>
       </c>
-      <c r="E18" s="5">
+      <c r="F18" s="6">
         <v>2.9378296910324</v>
       </c>
-      <c r="F18" s="6">
+      <c r="G18" s="7">
         <v>0.694172318512936</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4">
         <v>9233</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
+        <v>4011</v>
+      </c>
+      <c r="D19" s="4">
         <v>26486</v>
       </c>
-      <c r="D19" s="4">
+      <c r="E19" s="4">
         <v>6418</v>
       </c>
-      <c r="E19" s="5">
+      <c r="F19" s="6">
         <v>2.8686234160078</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="7">
         <v>0.695115347124445</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4">
         <v>16257</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
+        <v>7123</v>
+      </c>
+      <c r="D20" s="4">
         <v>68465</v>
       </c>
-      <c r="D20" s="4">
+      <c r="E20" s="4">
         <v>11408</v>
       </c>
-      <c r="E20" s="5">
+      <c r="F20" s="6">
         <v>4.21141662053269</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="7">
         <v>0.701728486190564</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4">
         <v>3143</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
+        <v>1496</v>
+      </c>
+      <c r="D21" s="4">
         <v>6633</v>
       </c>
-      <c r="D21" s="4">
+      <c r="E21" s="4">
         <v>2143</v>
       </c>
-      <c r="E21" s="5">
+      <c r="F21" s="6">
         <v>2.11040407254216</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="7">
         <v>0.681832643970729</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4">
         <v>1746</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
+        <v>805</v>
+      </c>
+      <c r="D22" s="4">
         <v>7566</v>
       </c>
-      <c r="D22" s="4">
+      <c r="E22" s="4">
         <v>1286</v>
       </c>
-      <c r="E22" s="5">
+      <c r="F22" s="6">
         <v>4.33333333333333</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="7">
         <v>0.736540664375716</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4">
         <v>5219</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
+        <v>2044</v>
+      </c>
+      <c r="D23" s="4">
         <v>22191</v>
       </c>
-      <c r="D23" s="4">
+      <c r="E23" s="4">
         <v>3708</v>
       </c>
-      <c r="E23" s="5">
+      <c r="F23" s="6">
         <v>4.25196397777352</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="7">
         <v>0.710480935045028</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4">
         <v>8168</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
+        <v>3754</v>
+      </c>
+      <c r="D24" s="4">
         <v>23250</v>
       </c>
-      <c r="D24" s="4">
+      <c r="E24" s="4">
         <v>5774</v>
       </c>
-      <c r="E24" s="5">
+      <c r="F24" s="6">
         <v>2.84647404505387</v>
       </c>
-      <c r="F24" s="6">
+      <c r="G24" s="7">
         <v>0.70690499510284</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="4">
         <v>2438</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
+        <v>1219</v>
+      </c>
+      <c r="D25" s="4">
         <v>4678</v>
       </c>
-      <c r="D25" s="4">
+      <c r="E25" s="4">
         <v>1607</v>
       </c>
-      <c r="E25" s="5">
+      <c r="F25" s="6">
         <v>1.91878589007383</v>
       </c>
-      <c r="F25" s="6">
+      <c r="G25" s="7">
         <v>0.659146841673503</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="4">
         <v>3080</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
+        <v>1611</v>
+      </c>
+      <c r="D26" s="4">
         <v>10224</v>
       </c>
-      <c r="D26" s="4">
+      <c r="E26" s="4">
         <v>1945</v>
       </c>
-      <c r="E26" s="5">
+      <c r="F26" s="6">
         <v>3.31948051948052</v>
       </c>
-      <c r="F26" s="6">
+      <c r="G26" s="7">
         <v>0.631493506493506</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4">
         <v>198</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
+        <v>103</v>
+      </c>
+      <c r="D27" s="4">
         <v>686</v>
       </c>
-      <c r="D27" s="4">
+      <c r="E27" s="4">
         <v>151</v>
       </c>
-      <c r="E27" s="5">
+      <c r="F27" s="6">
         <v>3.46464646464646</v>
       </c>
-      <c r="F27" s="6">
+      <c r="G27" s="7">
         <v>0.762626262626263</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="4">
         <v>4399</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
+        <v>2365</v>
+      </c>
+      <c r="D28" s="4">
         <v>8546</v>
       </c>
-      <c r="D28" s="4">
+      <c r="E28" s="4">
         <v>2849</v>
       </c>
-      <c r="E28" s="5">
+      <c r="F28" s="6">
         <v>1.94271425323937</v>
       </c>
-      <c r="F28" s="6">
+      <c r="G28" s="7">
         <v>0.64764719254376</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="4">
         <v>2803</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
+        <v>1483</v>
+      </c>
+      <c r="D29" s="4">
         <v>3944</v>
       </c>
-      <c r="D29" s="4">
+      <c r="E29" s="4">
         <v>1696</v>
       </c>
-      <c r="E29" s="5">
+      <c r="F29" s="6">
         <v>1.40706386014984</v>
       </c>
-      <c r="F29" s="6">
+      <c r="G29" s="7">
         <v>0.605066000713521</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="4">
         <v>664</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
+        <v>338</v>
+      </c>
+      <c r="D30" s="4">
         <v>1371</v>
       </c>
-      <c r="D30" s="4">
+      <c r="E30" s="4">
         <v>448</v>
       </c>
-      <c r="E30" s="5">
+      <c r="F30" s="6">
         <v>2.06475903614458</v>
       </c>
-      <c r="F30" s="6">
+      <c r="G30" s="7">
         <v>0.674698795180723</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="4">
         <v>1117</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
+        <v>569</v>
+      </c>
+      <c r="D31" s="4">
         <v>3059</v>
       </c>
-      <c r="D31" s="4">
+      <c r="E31" s="4">
         <v>781</v>
       </c>
-      <c r="E31" s="5">
+      <c r="F31" s="6">
         <v>2.73858549686661</v>
       </c>
-      <c r="F31" s="6">
+      <c r="G31" s="7">
         <v>0.699194270367055</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="4">
         <v>3256</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
+        <v>1715</v>
+      </c>
+      <c r="D32" s="4">
         <v>7443</v>
       </c>
-      <c r="D32" s="4">
+      <c r="E32" s="4">
         <v>1923</v>
       </c>
-      <c r="E32" s="5">
+      <c r="F32" s="6">
         <v>2.28593366093366</v>
       </c>
-      <c r="F32" s="6">
+      <c r="G32" s="7">
         <v>0.590601965601966</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="4">
         <v>29</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="8">
+        <v>6</v>
+      </c>
+      <c r="D33" s="4">
         <v>268</v>
       </c>
-      <c r="D33" s="7">
+      <c r="E33" s="9">
         <v>17</v>
       </c>
-      <c r="E33" s="5">
+      <c r="F33" s="6">
         <v>9.24137931034483</v>
       </c>
-      <c r="F33" s="6">
+      <c r="G33" s="7">
         <v>0.586206896551724</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="4">
         <v>11</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="5">
+        <v>5</v>
+      </c>
+      <c r="D34" s="4">
         <v>0</v>
       </c>
-      <c r="D34" s="4">
+      <c r="E34" s="4">
         <v>6</v>
       </c>
-      <c r="E34" s="5">
+      <c r="F34" s="6">
         <v>0</v>
       </c>
-      <c r="F34" s="6">
+      <c r="G34" s="7">
         <v>0.545454545454545</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:7">
       <c r="A35" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="4">
         <v>14</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="8">
+        <v>2</v>
+      </c>
+      <c r="D35" s="4">
         <v>49</v>
       </c>
-      <c r="D35" s="4">
+      <c r="E35" s="4">
         <v>11</v>
       </c>
-      <c r="E35" s="5">
+      <c r="F35" s="6">
         <v>3.5</v>
       </c>
-      <c r="F35" s="6">
+      <c r="G35" s="7">
         <v>0.785714285714286</v>
       </c>
     </row>
